--- a/data/Escenarios_Gx/320kW/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/320kW/simple_time_series.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Escenarios_Gx/320kW/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/320kW/simple_time_series.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenProfiles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Escenarios_Gx/320kW/simple_time_series.xlsx
+++ b/data/Escenarios_Gx/320kW/simple_time_series.xlsx
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,1071 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>C0593</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>C0554</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C0555</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C0556</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C0557</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C0558</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C0559</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C0560</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C0561</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C0562</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C0563</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C0564</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C0565</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C0527</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C0528</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C0529</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C0530</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C0531</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>C0532</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C0533</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C0534</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C0535</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C0536</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C0537</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C0538</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C0499</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C0500</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C0501</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C0502</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C0503</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C0504</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C0505</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C0506</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C0507</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C0508</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>C0509</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C0510</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C0472</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>C0473</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C0474</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>C0475</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>C0476</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>C0477</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>C0478</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C0479</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>C0480</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>C0481</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>C0482</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>C0483</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>C0440</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>C0441</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>C0442</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>C0443</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>C0444</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C0445</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>C0446</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>C0447</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>C0448</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>C0449</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>C0450</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>C0451</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>C0409</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>C0410</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>C0411</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>C0412</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>C0413</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>C0414</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>C0415</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>C0416</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>C0417</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>C0418</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>C0419</t>
         </is>
       </c>
     </row>
@@ -944,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,6 +2039,51 @@
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>station_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LH518B_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>station_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LH518B_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>station_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LH518B_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>station_1</t>
         </is>
@@ -990,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,89 +2418,927 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C0554</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C0555</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C0556</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C0557</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C0558</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C0559</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C0560</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>C0561</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>C0562</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C0563</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C0564</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C0565</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C0527</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>C0528</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C0529</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C0530</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>C0531</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C0532</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>C0533</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>C0534</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>C0535</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>C0536</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C0537</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C0538</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>C0499</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C0500</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>C0501</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C0502</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C0503</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C0504</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C0505</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C0506</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C0507</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C0508</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>C0509</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C0510</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C0472</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>C0473</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>C0474</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>C0475</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>C0476</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>C0477</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>C0478</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>C0479</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>C0480</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>C0481</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>C0482</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>C0483</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>C0440</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>C0441</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>C0442</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C0443</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>C0444</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>C0445</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>C0446</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>C0447</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>C0448</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>C0449</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>C0450</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>C0451</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>C0409</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>C0410</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>C0411</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>C0412</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>C0413</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>C0414</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>C0415</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>C0416</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>C0417</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>C0418</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>C0419</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
